--- a/public/documents/pieces-defense/RF-coefficient-liquide-solide.xlsx
+++ b/public/documents/pieces-defense/RF-coefficient-liquide-solide.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Recap fisc par exercice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Origine du coefficient" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cuisine fantome" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Effet de levier" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,14 +469,307 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Extrapolation de la cuisine - coefficient liquide -&gt; solide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Le CA cuisine n'est jamais mesure : il est obtenu en multipliant le CA liquides reconstitue par 2,94/3,02/3,10. Or ce coefficient EST le ratio solides/liquides de la propre caisse du restaurant : l'appliquer a un liquide gonfle recopie le gonflement sur la cuisine (cuisine fantome = 75 % du redressement) et amplifie x4 toute erreur sur les boissons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>CA liquides (apres abatt.)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>CA solides reconstitue</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Total reconstitue</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>CA declare</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Discordance</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>151590</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>445675</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>597265</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>404031</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>193234</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>143662</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>433860</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>577522</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>438658</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>138864</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>140306</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>434947</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>575253</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>435525</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>139728</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL 3 ans</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>435558</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1314482</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>1750040</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>1278214</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>471826</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Extrapolation de la cuisine - coefficient liquide -&gt; solide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Le CA cuisine n'est jamais mesure : il est obtenu en multipliant le CA liquides reconstitue par 2,94/3,02/3,10. Or ce coefficient EST le ratio solides/liquides de la propre caisse du restaurant : l'appliquer a un liquide gonfle recopie le gonflement sur la cuisine (cuisine fantome = 75 % du redressement) et amplifie x4 toute erreur sur les boissons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>CA liquides REEL (caisse)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CA solides REEL (caisse)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ratio solides/liquides reel</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Coefficient applique par le fisc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>102425</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>300747</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2.936</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>108919</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>329362</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.024</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>106113</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>329452</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.105</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,7 +782,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Le CA solides (cuisine) n'est pas mesure : il est obtenu en multipliant le CA liquides reconstitue par 2,94 / 3,02 / 3,10. Toute erreur sur les liquides est donc amplifiee ~3 fois.</t>
+          <t>Le CA cuisine n'est jamais mesure : il est obtenu en multipliant le CA liquides reconstitue par 2,94/3,02/3,10. Or ce coefficient EST le ratio solides/liquides de la propre caisse du restaurant : l'appliquer a un liquide gonfle recopie le gonflement sur la cuisine (cuisine fantome = 75 % du redressement) et amplifie x4 toute erreur sur les boissons.</t>
         </is>
       </c>
     </row>
@@ -498,22 +794,22 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>CA liquides (apres abatt.)</t>
+          <t>Cuisine REELLE (caisse)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>Cuisine reconstituee (fisc)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>CA solides</t>
+          <t>Cuisine fantome (ecart)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Total reconstitue</t>
+          <t>Gonflement du liquide</t>
         </is>
       </c>
     </row>
@@ -524,16 +820,18 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>151590</v>
+        <v>300747</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2.94</v>
+        <v>445675</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>445675</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>597265</v>
+        <v>144928</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>+48 %</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -543,16 +841,18 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>143662</v>
+        <v>329362</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3.02</v>
+        <v>433860</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>433860</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>577522</v>
+        <v>104498</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>+32 %</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -562,16 +862,18 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>140306</v>
+        <v>329452</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>3.1</v>
+        <v>434947</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>434947</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>575253</v>
+        <v>105495</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>+32 %</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -581,16 +883,124 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>435558</v>
+        <v>959561</v>
       </c>
       <c r="C8" s="7" t="n">
+        <v>1314482</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>354921</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Extrapolation de la cuisine - coefficient liquide -&gt; solide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Le CA cuisine n'est jamais mesure : il est obtenu en multipliant le CA liquides reconstitue par 2,94/3,02/3,10. Or ce coefficient EST le ratio solides/liquides de la propre caisse du restaurant : l'appliquer a un liquide gonfle recopie le gonflement sur la cuisine (cuisine fantome = 75 % du redressement) et amplifie x4 toute erreur sur les boissons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Levier sur le total (1 + coef)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>1 EUR de liquide sur-estime -&gt; 3,94 EUR de redressement</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>3.02</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>1314482</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>1750040</v>
+      <c r="C6" s="5" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1 EUR de liquide sur-estime -&gt; 4,02 EUR de redressement</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1 EUR de liquide sur-estime -&gt; 4,10 EUR de redressement</t>
+        </is>
       </c>
     </row>
   </sheetData>
